--- a/PillTime-DB.xlsx
+++ b/PillTime-DB.xlsx
@@ -565,7 +565,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>En Apps Script ve a Configuración del proyecto y pon la zona horaria correcta (America/Mexico_City).</t>
+          <t>En Apps Script ve a Configuración del proyecto y pon la zona horaria correcta (America/Bogota).</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>America/Mexico_City</t>
+          <t>America/Bogota</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
